--- a/selenium_day_2026_07_17/fake_user_data.xlsx
+++ b/selenium_day_2026_07_17/fake_user_data.xlsx
@@ -446,280 +446,280 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Samuel Griffith</t>
+          <t>Tanya Johnson</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>larrycooley@example.com</t>
+          <t>jphillips@example.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>001-653-525-0822x68171</t>
+          <t>416.461.9257x9582</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>87898 Jasmine Path Suite 241
-North Cheryl, MP 98194</t>
+          <t>492 Burnett Lights Suite 866
+New Ericfort, MN 80299</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Barnes PLC</t>
+          <t>Sanders, Ferguson and James</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Summer Schneider</t>
+          <t>Erin Friedman</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>yjacobs@example.net</t>
+          <t>awhite@example.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>836-726-8379x71286</t>
+          <t>(968)625-3253</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>806 Watson Trace Apt. 577
-New Jessica, NH 61391</t>
+          <t>3477 Lawrence Springs Apt. 796
+North Brandimouth, AZ 70154</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Holder PLC</t>
+          <t>Brooks, Reyes and Herring</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jennifer Martinez</t>
+          <t>Elizabeth Fisher</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>matthew83@example.com</t>
+          <t>bradley20@example.org</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>344-634-4477</t>
+          <t>825.978.9316x498</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>750 Strong Corners Apt. 793
-Lake Jefferymouth, AR 63342</t>
+          <t>76872 Wood Plaza Suite 743
+North Cynthia, SC 73485</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chavez-Hoffman</t>
+          <t>Wade, Hayden and Morse</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abigail Johnson</t>
+          <t>James Moore</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sbrown@example.org</t>
+          <t>patricia67@example.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>442.620.9936x6249</t>
+          <t>+1-650-504-5319</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29177 Ford Springs Apt. 903
-North Barbarastad, MP 24646</t>
+          <t>822 Evan Motorway Suite 387
+Blackville, MN 52346</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jackson, Rios and Anderson</t>
+          <t>Pollard-Torres</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Abigail Hawkins</t>
+          <t>Shawn Murphy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ellenmelton@example.com</t>
+          <t>evanhunt@example.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+1-801-320-2117x9357</t>
+          <t>+1-743-829-4267x14429</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7961 Christopher Point Suite 379
-Port Timothy, SD 57207</t>
+          <t>546 Brianna Lakes Suite 549
+South Edwardmouth, ME 12742</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Clark, Pierce and Crawford</t>
+          <t>Rush, Knight and Christensen</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Denise Parsons</t>
+          <t>Billy Baldwin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>carolhutchinson@example.org</t>
+          <t>margaret77@example.net</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>001-701-486-2431x802</t>
+          <t>001-237-297-7933</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>484 David Stream
-East Jonathan, GU 71385</t>
+          <t>325 Armstrong Parks
+Lambertview, NJ 26008</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meyer, Diaz and Johnson</t>
+          <t>Sharp, Miller and Ross</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Christine Walker</t>
+          <t>Eric Diaz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gary80@example.net</t>
+          <t>stevenedwards@example.net</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>251-842-5154</t>
+          <t>932-926-8489x9016</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>140 Ford Circles Apt. 441
-Kristyhaven, AL 70578</t>
+          <t>13382 Michelle Glen Suite 331
+Karenshire, MA 57007</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Price Inc</t>
+          <t>Sweeney, Hood and Williams</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sean Carter</t>
+          <t>Lynn Michael</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>margaret65@example.net</t>
+          <t>justinmendoza@example.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>729.280.1780x905</t>
+          <t>+1-201-741-1513</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PSC 2042, Box 9047
-APO AE 36288</t>
+          <t>3582 Connor Shoal Suite 638
+Paulbury, MO 09362</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Harding PLC</t>
+          <t>Chavez, Rodriguez and Durham</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dawn Davila</t>
+          <t>Bonnie Harris</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>smithmichael@example.org</t>
+          <t>kurttaylor@example.org</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7506632566</t>
+          <t>(773)221-3601x320</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>021 Serrano Glens
-Joshuashire, CT 49262</t>
+          <t>440 Miller Ways Suite 145
+Foxland, MH 37071</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wilkerson-Hamilton</t>
+          <t>Mclean-Morrow</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nicole Richards</t>
+          <t>Wendy Gomez</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>heather73@example.com</t>
+          <t>annmcguire@example.org</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3033427797</t>
+          <t>283.392.2428x7864</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31484 Kaitlyn Courts Suite 558
-Reyesfurt, NE 84267</t>
+          <t>969 Ramos Harbor Suite 642
+Englishchester, FL 73717</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Johnson-Rodriguez</t>
+          <t>Murphy LLC</t>
         </is>
       </c>
     </row>
